--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487611_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487611_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.948700000000001</v>
+        <v>9.1595</v>
       </c>
       <c r="E2" t="n">
-        <v>9.041499999999999</v>
+        <v>8.061500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9072</v>
+        <v>1.098</v>
       </c>
       <c r="G2" t="n">
         <v>5.7073</v>
@@ -610,13 +610,13 @@
         <v>2.3284</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3295</v>
+        <v>0.5403</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4098</v>
+        <v>0.4298</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0803</v>
+        <v>0.1105</v>
       </c>
       <c r="V2" t="n">
         <v>1.5537</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7279</v>
+        <v>1.9643</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5258</v>
+        <v>1.6259</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2021</v>
+        <v>0.3384</v>
       </c>
       <c r="G3" t="n">
         <v>0.2674</v>
@@ -688,13 +688,13 @@
         <v>1.1642</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9275</v>
+        <v>-0.6912</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3511</v>
+        <v>-0.251</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5765</v>
+        <v>-0.4402</v>
       </c>
       <c r="V3" t="n">
         <v>1.2239</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. SANTANA DE LA ROSA</t>
+          <t>S. HERRERO GALVEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.504</v>
+        <v>-0.9243</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.3004</v>
+        <v>-0.8973</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7965</v>
+        <v>-0.0271</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7982</v>
+        <v>0.1944</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7678</v>
+        <v>0.061</v>
       </c>
       <c r="I4" t="n">
-        <v>1.566</v>
+        <v>0.1335</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1015</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7332</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6318</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8996</v>
+        <v>0.1944</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0346</v>
+        <v>0.061</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9343</v>
+        <v>0.1335</v>
       </c>
       <c r="P4" t="n">
         <v>-0.9702</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9702</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8919</v>
+        <v>-0.1486</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7413</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1505</v>
+        <v>-0.2215</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. HERRERO GALVEZ</t>
+          <t>H. SANTANA DE LA ROSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9516</v>
+        <v>-1.1168</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8973</v>
+        <v>-1.9406</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0543</v>
+        <v>0.8237</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1944</v>
+        <v>0.7982</v>
       </c>
       <c r="H5" t="n">
-        <v>0.061</v>
+        <v>-0.7678</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1335</v>
+        <v>1.566</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0.1015</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0.7332</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.6318</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1944</v>
+        <v>0.8996</v>
       </c>
       <c r="N5" t="n">
-        <v>0.061</v>
+        <v>-0.0346</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1335</v>
+        <v>0.9343</v>
       </c>
       <c r="P5" t="n">
         <v>-0.9702</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.9702</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1759</v>
+        <v>0.279</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.1012</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2488</v>
+        <v>0.1778</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.473</v>
+        <v>-1.4458</v>
       </c>
       <c r="E6" t="n">
         <v>-1.3223</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1507</v>
+        <v>-0.1235</v>
       </c>
       <c r="G6" t="n">
         <v>-1.4912</v>
@@ -922,13 +922,13 @@
         <v>0.3881</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3699</v>
+        <v>-0.3426</v>
       </c>
       <c r="T6" t="n">
         <v>0.0123</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3822</v>
+        <v>-0.355</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. LOPEZ RIVERA</t>
+          <t>A. GOMEZ SERRANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1463</v>
+        <v>-1.7427</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.929</v>
+        <v>-0.8182</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2174</v>
+        <v>-0.9244</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.195</v>
+        <v>-2.604</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1106</v>
+        <v>0.2678</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0844</v>
+        <v>-2.8718</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6261</v>
+        <v>-0.3101</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6261</v>
+        <v>1.6107</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.9208</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5689</v>
+        <v>-2.2939</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4844</v>
+        <v>-1.3429</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0844</v>
+        <v>-0.951</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5821</v>
+        <v>1.9403</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5821</v>
+        <v>1.9403</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5334</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3028</v>
+        <v>-0.5081</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2306</v>
+        <v>-0.2888</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
+          <t>R. LOPEZ RIVERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1671</v>
+        <v>-1.9917</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.2689</v>
+        <v>-0.8289</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1018</v>
+        <v>-1.1629</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.7994</v>
+        <v>-2.195</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1116</v>
+        <v>-1.1106</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6878</v>
+        <v>-1.0844</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1028</v>
+        <v>-0.6261</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6962</v>
+        <v>-0.6261</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.799</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6966</v>
+        <v>-1.5689</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.8078</v>
+        <v>-0.4844</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1112</v>
+        <v>-1.0844</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.5821</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9105</v>
+        <v>0.5821</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1263</v>
+        <v>-0.3788</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.2027</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8879</v>
+        <v>-0.1761</v>
       </c>
       <c r="V8" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GOMEZ SERRANO</t>
+          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3338</v>
+        <v>-2.2814</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2186</v>
+        <v>-2.6473</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1152</v>
+        <v>0.3659</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.604</v>
+        <v>-3.7994</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2678</v>
+        <v>-2.1116</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.8718</v>
+        <v>-1.6878</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3101</v>
+        <v>-1.1028</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6107</v>
+        <v>0.6962</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9208</v>
+        <v>-1.799</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2939</v>
+        <v>-2.6966</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3429</v>
+        <v>-2.8078</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.951</v>
+        <v>0.1112</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9403</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9403</v>
+        <v>2.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3881</v>
+        <v>0.0121</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9085</v>
+        <v>-0.14</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4796</v>
+        <v>0.152</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2821</v>
+        <v>1.506</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6796</v>
+        <v>-2.683</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6525</v>
+        <v>-1.7921</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0272</v>
+        <v>-0.8909</v>
       </c>
       <c r="G10" t="n">
         <v>-4.4744</v>
@@ -1234,13 +1234,13 @@
         <v>2.3284</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2232</v>
+        <v>-0.2266</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1233</v>
+        <v>-0.0163</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3465</v>
+        <v>-0.2103</v>
       </c>
       <c r="V10" t="n">
         <v>0.6597</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5204</v>
+        <v>-3.1803</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9138</v>
+        <v>-2.192</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6067</v>
+        <v>-0.9882</v>
       </c>
       <c r="G11" t="n">
         <v>-4.647</v>
@@ -1312,13 +1312,13 @@
         <v>3.2985</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4854</v>
+        <v>-0.1452</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1373</v>
+        <v>-0.4156</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6519</v>
+        <v>0.2703</v>
       </c>
       <c r="V11" t="n">
         <v>1.2239</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6475</v>
+        <v>-3.9934</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5544</v>
+        <v>-3.9548</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0931</v>
+        <v>-0.0386</v>
       </c>
       <c r="G12" t="n">
         <v>-2.753</v>
@@ -1390,13 +1390,13 @@
         <v>0.5821</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1339</v>
+        <v>-0.212</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3645</v>
+        <v>-0.0359</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2306</v>
+        <v>-0.1761</v>
       </c>
       <c r="V12" t="n">
         <v>0.3299</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.4133</v>
+        <v>-7.3189</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.199199999999999</v>
+        <v>-8.3774</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7859</v>
+        <v>1.0585</v>
       </c>
       <c r="G13" t="n">
         <v>-5.0665</v>
@@ -1468,13 +1468,13 @@
         <v>1.9403</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4065</v>
+        <v>-0.3121</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8838</v>
+        <v>-0.062</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5226</v>
+        <v>-0.2501</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-16.16</v>
+        <v>-15.5545</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.6891</v>
+        <v>-15.0835</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4711000000000001</v>
+        <v>-0.4710999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-20.0632</v>
@@ -1546,13 +1546,13 @@
         <v>18.4331</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.0283</v>
+        <v>-2.4226</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.621</v>
+        <v>-1.0154</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.4074</v>
+        <v>-1.4075</v>
       </c>
       <c r="V14" t="n">
         <v>4.9911</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4814</v>
+        <v>6.7065</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5834</v>
+        <v>2.4843</v>
       </c>
       <c r="F15" t="n">
-        <v>3.898</v>
+        <v>4.2222</v>
       </c>
       <c r="G15" t="n">
         <v>4.4266</v>
@@ -1624,13 +1624,13 @@
         <v>2.1344</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6736</v>
+        <v>0.5515</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7020999999999999</v>
+        <v>0.1988</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0285</v>
+        <v>0.3528</v>
       </c>
       <c r="V15" t="n">
         <v>0.5642</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MUNRO</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.9369</v>
+        <v>5.0504</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8227</v>
+        <v>1.5034</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1142</v>
+        <v>3.5471</v>
       </c>
       <c r="G16" t="n">
-        <v>4.5004</v>
+        <v>2.9</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1134</v>
+        <v>3.92</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3869</v>
+        <v>-1.02</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9795</v>
+        <v>2.4457</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6982</v>
+        <v>3.6992</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2813</v>
+        <v>-1.2535</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5208</v>
+        <v>0.4543</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4152</v>
+        <v>0.2208</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1056</v>
+        <v>0.2335</v>
       </c>
       <c r="P16" t="n">
         <v>-0.3881</v>
@@ -1702,28 +1702,28 @@
         <v>2.5224</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8246</v>
+        <v>0.7027</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7537</v>
+        <v>-0.1498</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0709</v>
+        <v>0.8524</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.8358</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.1179</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>J. MUNRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.7825</v>
+        <v>4.6333</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9028</v>
+        <v>1.2221</v>
       </c>
       <c r="F17" t="n">
-        <v>3.8797</v>
+        <v>3.4111</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9</v>
+        <v>4.5004</v>
       </c>
       <c r="H17" t="n">
-        <v>3.92</v>
+        <v>3.1134</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.02</v>
+        <v>1.3869</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4457</v>
+        <v>3.9795</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6992</v>
+        <v>2.6982</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2535</v>
+        <v>1.2813</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4543</v>
+        <v>0.5208</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2208</v>
+        <v>0.4152</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2335</v>
+        <v>0.1056</v>
       </c>
       <c r="P17" t="n">
         <v>-0.3881</v>
@@ -1780,28 +1780,28 @@
         <v>2.5224</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4348</v>
+        <v>0.521</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7504</v>
+        <v>0.1531</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1851</v>
+        <v>0.3679</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8358</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1179</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MENDOZA ALVAREZ</t>
+          <t>E. ECHEVERRIA MATEO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.7172</v>
+        <v>3.3242</v>
       </c>
       <c r="E18" t="n">
-        <v>4.2823</v>
+        <v>-2.0727</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5651</v>
+        <v>5.3969</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3792</v>
+        <v>3.304</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7195</v>
+        <v>4.3706</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3402</v>
+        <v>-1.0667</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4079</v>
+        <v>1.7154</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7425</v>
+        <v>3.555</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3347</v>
+        <v>-1.8396</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0286</v>
+        <v>1.5885</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0231</v>
+        <v>0.8156</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0056</v>
+        <v>0.7729</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9702</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.8806</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9702</v>
+        <v>3.2985</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5917</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>3.5923</v>
+        <v>0.0925</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0007</v>
+        <v>0.5098</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. ECHEVERRIA MATEO</t>
+          <t>J. PRATS PEINADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5929</v>
+        <v>2.5152</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6733</v>
+        <v>1.0704</v>
       </c>
       <c r="F19" t="n">
-        <v>5.2662</v>
+        <v>1.4448</v>
       </c>
       <c r="G19" t="n">
-        <v>3.304</v>
+        <v>1.8481</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3706</v>
+        <v>-0.4548</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0667</v>
+        <v>2.3029</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7154</v>
+        <v>1.4879</v>
       </c>
       <c r="K19" t="n">
-        <v>3.555</v>
+        <v>-0.4202</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.8396</v>
+        <v>1.908</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5885</v>
+        <v>0.3602</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8156</v>
+        <v>-0.0346</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7729</v>
+        <v>0.3948</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.8806</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>3.2985</v>
+        <v>1.1642</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.129</v>
+        <v>0.1909</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5081</v>
+        <v>0.2706</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3791</v>
+        <v>-0.0796</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PRATS PEINADO</t>
+          <t>J. MENDOZA ALVAREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6086</v>
+        <v>1.5028</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5699</v>
+        <v>1.8799</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0388</v>
+        <v>-0.3771</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8481</v>
+        <v>0.3792</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4548</v>
+        <v>1.7195</v>
       </c>
       <c r="I20" t="n">
-        <v>2.3029</v>
+        <v>-1.3402</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4879</v>
+        <v>0.4079</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4202</v>
+        <v>1.7425</v>
       </c>
       <c r="L20" t="n">
-        <v>1.908</v>
+        <v>-1.3347</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3602</v>
+        <v>-0.0286</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0346</v>
+        <v>-0.0231</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3948</v>
+        <v>-0.0056</v>
       </c>
       <c r="P20" t="n">
-        <v>0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7156</v>
+        <v>1.3773</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2299</v>
+        <v>1.19</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4856</v>
+        <v>0.1873</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2821</v>
+        <v>-1.2239</v>
       </c>
       <c r="W20" t="n">
         <v>0.2821</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. DE LA CRUZ DE LA ROSA</t>
+          <t>G. HIERRO ABAD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.482</v>
+        <v>-1.1647</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8508</v>
+        <v>-0.8771</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6312</v>
+        <v>-0.2876</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6665</v>
+        <v>2.4652</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5569</v>
+        <v>0.6484</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2235</v>
+        <v>1.8168</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0577</v>
+        <v>1.344</v>
       </c>
       <c r="K21" t="n">
-        <v>0.725</v>
+        <v>0.5726</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6673</v>
+        <v>0.7713</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7242</v>
+        <v>1.1212</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1681</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5561</v>
+        <v>1.0454</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.194</v>
+        <v>0.3881</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7761</v>
+        <v>2.3284</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2725</v>
+        <v>-0.3463</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0617</v>
+        <v>-0.2807</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2109</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.894</v>
+        <v>-3.6716</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.894</v>
+        <v>-3.6716</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>A. DE LAS HERAS SANZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6327</v>
+        <v>-1.3279</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.635</v>
+        <v>-0.9530999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0022</v>
+        <v>-0.3748</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7075</v>
+        <v>0.1987</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-0.0626</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3864</v>
+        <v>0.2614</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0804</v>
+        <v>0.7003</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5108</v>
+        <v>0.7003</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5911999999999999</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6271</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1681</v>
+        <v>-0.7629</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7952</v>
+        <v>0.2614</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.1344</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7761</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.018</v>
+        <v>0.1032</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1951</v>
+        <v>-0.0236</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8228</v>
+        <v>0.1267</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2239</v>
+        <v>-0.6597</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. DE LAS HERAS SANZ</t>
+          <t>L. DE LA CRUZ DE LA ROSA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7828</v>
+        <v>-1.7851</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3535</v>
+        <v>-1.1511</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4293</v>
+        <v>-0.634</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1987</v>
+        <v>-0.6665</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0626</v>
+        <v>0.5569</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2614</v>
+        <v>-1.2235</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7003</v>
+        <v>0.0577</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7003</v>
+        <v>0.725</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.6673</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-0.7242</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7629</v>
+        <v>-0.1681</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2614</v>
+        <v>-0.5561</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.7761</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3517</v>
+        <v>-0.0306</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.424</v>
+        <v>-0.2386</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0722</v>
+        <v>0.2081</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6597</v>
+        <v>-0.894</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. HIERRO ABAD</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0617</v>
+        <v>-1.9598</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1774</v>
+        <v>-2.635</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8844</v>
+        <v>0.6752</v>
       </c>
       <c r="G24" t="n">
-        <v>2.4652</v>
+        <v>0.7075</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6484</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8168</v>
+        <v>1.3864</v>
       </c>
       <c r="J24" t="n">
-        <v>1.344</v>
+        <v>0.0804</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5726</v>
+        <v>-0.5108</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7713</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1212</v>
+        <v>0.6271</v>
       </c>
       <c r="N24" t="n">
-        <v>0.07580000000000001</v>
+        <v>-0.1681</v>
       </c>
       <c r="O24" t="n">
-        <v>1.0454</v>
+        <v>0.7952</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3881</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3284</v>
+        <v>0.7761</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2434</v>
+        <v>0.6909</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.581</v>
+        <v>0.1951</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6624</v>
+        <v>0.4958</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.6716</v>
+        <v>-1.2239</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.6716</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>16.1603</v>
+        <v>17.49489999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4711000000000007</v>
+        <v>0.4711000000000003</v>
       </c>
       <c r="F25" t="n">
-        <v>15.6891</v>
+        <v>17.0238</v>
       </c>
       <c r="G25" t="n">
         <v>20.0632</v>
@@ -2374,7 +2374,7 @@
         <v>16.7822</v>
       </c>
       <c r="I25" t="n">
-        <v>3.280900000000001</v>
+        <v>3.2809</v>
       </c>
       <c r="J25" t="n">
         <v>14.6282</v>
@@ -2389,10 +2389,10 @@
         <v>5.435</v>
       </c>
       <c r="N25" t="n">
-        <v>0.9308000000000001</v>
+        <v>0.9308</v>
       </c>
       <c r="O25" t="n">
-        <v>4.5041</v>
+        <v>4.504100000000001</v>
       </c>
       <c r="P25" t="n">
         <v>-1.9404</v>
@@ -2404,19 +2404,19 @@
         <v>16.4927</v>
       </c>
       <c r="S25" t="n">
-        <v>3.028299999999999</v>
+        <v>4.3629</v>
       </c>
       <c r="T25" t="n">
-        <v>1.4073</v>
+        <v>1.4074</v>
       </c>
       <c r="U25" t="n">
-        <v>1.6208</v>
+        <v>2.9556</v>
       </c>
       <c r="V25" t="n">
         <v>-4.991</v>
       </c>
       <c r="W25" t="n">
-        <v>2.868600000000001</v>
+        <v>2.8686</v>
       </c>
       <c r="X25" t="n">
         <v>-7.8597</v>
